--- a/public/template_valores_iniciais.xlsx
+++ b/public/template_valores_iniciais.xlsx
@@ -26,8 +26,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Inter"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,7 +45,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,14 +53,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,36 +441,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Codigo Contrato</t>
@@ -467,110 +484,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Percentual Reajuste (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Valor Enfermaria</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Valor Apartamento</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Enf 0-18</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Enf 19-23</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Enf 24-28</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Enf 29-33</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enf 34-38</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Enf 39-43</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Enf 44-48</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Enf 49-53</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Enf 54-58</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Enf 59+</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Apt 0-18</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Apt 19-23</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Apt 24-28</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Apt 29-33</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Apt 34-38</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Apt 39-43</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Apt 44-48</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Apt 49-53</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Apt 54-58</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Apt 59+</t>
         </is>
@@ -584,74 +606,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EMPRESA EXEMPLO LTDA</t>
+          <t>Empresa Exemplo LTDA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>450</v>
+        <v>8.5</v>
       </c>
       <c r="D2" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="E2" t="n">
-        <v>200</v>
+        <v>520</v>
       </c>
       <c r="F2" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="G2" t="n">
+        <v>210</v>
+      </c>
+      <c r="H2" t="n">
         <v>240</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
+        <v>270</v>
+      </c>
+      <c r="J2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K2" t="n">
+        <v>340</v>
+      </c>
+      <c r="L2" t="n">
+        <v>380</v>
+      </c>
+      <c r="M2" t="n">
+        <v>430</v>
+      </c>
+      <c r="N2" t="n">
+        <v>490</v>
+      </c>
+      <c r="O2" t="n">
+        <v>580</v>
+      </c>
+      <c r="P2" t="n">
         <v>260</v>
       </c>
-      <c r="I2" t="n">
-        <v>290</v>
-      </c>
-      <c r="J2" t="n">
-        <v>330</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="Q2" t="n">
+        <v>300</v>
+      </c>
+      <c r="R2" t="n">
+        <v>340</v>
+      </c>
+      <c r="S2" t="n">
         <v>380</v>
       </c>
-      <c r="L2" t="n">
-        <v>440</v>
-      </c>
-      <c r="M2" t="n">
-        <v>510</v>
-      </c>
-      <c r="N2" t="n">
-        <v>600</v>
-      </c>
-      <c r="O2" t="n">
-        <v>300</v>
-      </c>
-      <c r="P2" t="n">
-        <v>330</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>360</v>
-      </c>
-      <c r="R2" t="n">
-        <v>400</v>
-      </c>
-      <c r="S2" t="n">
-        <v>450</v>
-      </c>
       <c r="T2" t="n">
-        <v>510</v>
+        <v>430</v>
       </c>
       <c r="U2" t="n">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="V2" t="n">
-        <v>670</v>
+        <v>540</v>
       </c>
       <c r="W2" t="n">
-        <v>770</v>
+        <v>610</v>
       </c>
       <c r="X2" t="n">
-        <v>900</v>
+        <v>690</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>820</v>
       </c>
     </row>
   </sheetData>

--- a/public/template_valores_iniciais.xlsx
+++ b/public/template_valores_iniciais.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valores Iniciais" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruções" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +27,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Inter"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +55,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002D5A3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C65911"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,26 +83,65 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,245 +508,569 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:A30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COMO PREENCHER A PLANILHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1. IDENTIFICAÇÃO (obrigatório)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Código Contrato: prioridade para localizar a empresa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nome Empresa: usado se o código estiver vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2. PERCENTUAL DE REAJUSTE (opcional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Informe em % (ex: 10 = 10%). Os valores informados são considerados VALOR ATUAL (antes do reajuste).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • O sistema aplica o percentual automaticamente e grava o reajuste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Deixe 0 ou em branco se não quiser aplicar reajuste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>3. COMO O SISTEMA IDENTIFICA O TIPO DE CONTRATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ➤ Contrato COM VALOR FIXO: preencha apenas 'Valor Enfermaria' e/ou 'Valor Apartamento'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Deixe as 20 colunas de faixa etária em branco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ➤ Contrato POR FAIXA ETÁRIA: deixe 'Valor Enfermaria'/'Valor Apartamento' em branco (ou 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     e preencha as 10 faixas correspondentes (Enf 0-18 ... Enf 59+ e/ou Apt 0-18 ... Apt 59+).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ➤ Contrato MISTO: pode combinar (ex: enfermaria por faixa + apartamento valor fixo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>4. MODALIDADES (Enfermaria / Apartamento)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Se a empresa só tem ENFERMARIA: preencha apenas as colunas de Enfermaria, deixe Apartamento em branco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Se a empresa só tem APARTAMENTO: preencha apenas as colunas de Apartamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>5. FAIXAS ETÁRIAS ANS (padrão)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   0-18, 19-23, 24-28, 29-33, 34-38, 39-43, 44-48, 49-53, 54-58, 59+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>6. FORMATO DE VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Use ponto ou vírgula como separador decimal (ex: 250.00 ou 250,00).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Não use 'R$' nem separador de milhar.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Codigo Contrato</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>IDENTIFICAÇÃO</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>REAJUSTE</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>CONTRATO COM VALOR FIXO (preencha só se NÃO for por faixa etária)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>CONTRATO POR FAIXA ETÁRIA - ENFERMARIA (preencha as 10 faixas)</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>CONTRATO POR FAIXA ETÁRIA - APARTAMENTO (preencha as 10 faixas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Código Contrato</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Nome Empresa</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Percentual Reajuste (%)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Valor Enfermaria</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Valor Apartamento</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Enf 0-18</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Enf 19-23</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Enf 24-28</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Enf 29-33</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Enf 34-38</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Enf 39-43</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Enf 44-48</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>Enf 49-53</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N2" s="8" t="inlineStr">
         <is>
           <t>Enf 54-58</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>Enf 59+</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>Apt 0-18</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>Apt 19-23</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R2" s="8" t="inlineStr">
         <is>
           <t>Apt 24-28</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>Apt 29-33</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>Apt 34-38</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>Apt 39-43</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>Apt 44-48</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W2" s="8" t="inlineStr">
         <is>
           <t>Apt 49-53</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X2" s="8" t="inlineStr">
         <is>
           <t>Apt 54-58</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y2" s="8" t="inlineStr">
         <is>
           <t>Apt 59+</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Empresa Exemplo LTDA</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D2" t="n">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Empresa Exemplo (valor fixo)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>380</v>
+      </c>
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="12" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr"/>
+      <c r="I3" s="12" t="inlineStr"/>
+      <c r="J3" s="12" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
+      <c r="M3" s="12" t="inlineStr"/>
+      <c r="N3" s="12" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr"/>
+      <c r="P3" s="12" t="inlineStr"/>
+      <c r="Q3" s="12" t="inlineStr"/>
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr"/>
+      <c r="T3" s="12" t="inlineStr"/>
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr"/>
+      <c r="W3" s="12" t="inlineStr"/>
+      <c r="X3" s="12" t="inlineStr"/>
+      <c r="Y3" s="12" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Empresa Exemplo (faixa etária)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="14" t="inlineStr"/>
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="M4" s="14" t="n">
+        <v>360</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>430</v>
+      </c>
+      <c r="O4" s="14" t="n">
+        <v>520</v>
+      </c>
+      <c r="P4" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q4" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="R4" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="S4" s="14" t="n">
+        <v>270</v>
+      </c>
+      <c r="T4" s="14" t="n">
+        <v>310</v>
+      </c>
+      <c r="U4" s="14" t="n">
+        <v>370</v>
+      </c>
+      <c r="V4" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="W4" s="14" t="n">
+        <v>520</v>
+      </c>
+      <c r="X4" s="14" t="n">
+        <v>620</v>
+      </c>
+      <c r="Y4" s="14" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Empresa Exemplo (só enfermaria por faixa)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="12" t="inlineStr"/>
+      <c r="E5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>170</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>290</v>
+      </c>
+      <c r="M5" s="12" t="n">
         <v>350</v>
       </c>
-      <c r="E2" t="n">
-        <v>520</v>
-      </c>
-      <c r="F2" t="n">
-        <v>180</v>
-      </c>
-      <c r="G2" t="n">
-        <v>210</v>
-      </c>
-      <c r="H2" t="n">
-        <v>240</v>
-      </c>
-      <c r="I2" t="n">
-        <v>270</v>
-      </c>
-      <c r="J2" t="n">
-        <v>300</v>
-      </c>
-      <c r="K2" t="n">
-        <v>340</v>
-      </c>
-      <c r="L2" t="n">
-        <v>380</v>
-      </c>
-      <c r="M2" t="n">
-        <v>430</v>
-      </c>
-      <c r="N2" t="n">
-        <v>490</v>
-      </c>
-      <c r="O2" t="n">
-        <v>580</v>
-      </c>
-      <c r="P2" t="n">
-        <v>260</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>300</v>
-      </c>
-      <c r="R2" t="n">
-        <v>340</v>
-      </c>
-      <c r="S2" t="n">
-        <v>380</v>
-      </c>
-      <c r="T2" t="n">
-        <v>430</v>
-      </c>
-      <c r="U2" t="n">
-        <v>480</v>
-      </c>
-      <c r="V2" t="n">
-        <v>540</v>
-      </c>
-      <c r="W2" t="n">
-        <v>610</v>
-      </c>
-      <c r="X2" t="n">
-        <v>690</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>820</v>
-      </c>
+      <c r="N5" s="12" t="n">
+        <v>420</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>510</v>
+      </c>
+      <c r="P5" s="12" t="inlineStr"/>
+      <c r="Q5" s="12" t="inlineStr"/>
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr"/>
+      <c r="T5" s="12" t="inlineStr"/>
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr"/>
+      <c r="W5" s="12" t="inlineStr"/>
+      <c r="X5" s="12" t="inlineStr"/>
+      <c r="Y5" s="12" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="P1:Y1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:O1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>